--- a/test-data/test_contacts.xlsx
+++ b/test-data/test_contacts.xlsx
@@ -25,12 +25,12 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Work Phone</t>
+          <t>Phone1</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Secondary Phone</t>
+          <t>Phone2</t>
         </is>
       </c>
     </row>

--- a/test-data/test_contacts.xlsx
+++ b/test-data/test_contacts.xlsx
@@ -47,22 +47,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>C IT</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>james.carter@example.com</t>
+          <t>james.carter@office.com</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>+1-555-0101</t>
+          <t>0701000000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>+1-555-0201</t>
+          <t>081000000</t>
         </is>
       </c>
     </row>
@@ -84,17 +84,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>olivia.bennett@example.com</t>
+          <t>olivia.bennett@office.com</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>+1-555-0102</t>
+          <t>0721000037</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>+1-555-0202</t>
+          <t>081000053</t>
         </is>
       </c>
     </row>
@@ -116,17 +116,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ethan.walker@example.com</t>
+          <t>ethan.walker@office.com</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>+1-555-0103</t>
+          <t>0731000074</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>+1-555-0203</t>
+          <t>081000106</t>
         </is>
       </c>
     </row>
@@ -148,17 +148,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>sophia.turner@example.com</t>
+          <t>sophia.turner@office.com</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>+1-555-0104</t>
+          <t>0761000111</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>+1-555-0204</t>
+          <t>081000159</t>
         </is>
       </c>
     </row>
@@ -180,17 +180,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>liam.foster@example.com</t>
+          <t>liam.foster@office.com</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>+1-555-0105</t>
+          <t>0701000148</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>+1-555-0205</t>
+          <t>081000212</t>
         </is>
       </c>
     </row>
@@ -212,17 +212,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ava.mitchell@example.com</t>
+          <t>ava.mitchell@office.com</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>+1-555-0106</t>
+          <t>0721000185</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>+1-555-0206</t>
+          <t>081000265</t>
         </is>
       </c>
     </row>
@@ -244,125 +244,125 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>noah.coleman@example.com</t>
+          <t>noah.coleman@office.com</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>+1-555-0107</t>
+          <t>0731000222</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>+1-555-0207</t>
+          <t>081000318</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Reynolds</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mia</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>C Logistics</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>mia.reynolds@example.com</t>
+          <t>mason.price@office.com</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>+1-555-0108</t>
+          <t>0761000259</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>+1-555-0208</t>
+          <t>081000371</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>Barnes</t>
+          <t>Simmons</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>lucas.barnes@example.com</t>
+          <t>charlotte.simmons@office.com</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>+1-555-0109</t>
+          <t>0701000296</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>+1-555-0209</t>
+          <t>081000424</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>isabella.hayes@example.com</t>
+          <t>benjamin.ross@office.com</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>+1-555-0110</t>
+          <t>0721000333</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>+1-555-0210</t>
+          <t>081000477</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Bryant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -372,317 +372,317 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>mason.price@example.com</t>
+          <t>amelia.bryant@office.com</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>+1-555-0111</t>
+          <t>0731000370</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>+1-555-0211</t>
+          <t>081000530</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Simmons</t>
+          <t>Sanders</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>C Production</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>charlotte.simmons@example.com</t>
+          <t>henry.sanders@office.com</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>+1-555-0112</t>
+          <t>0761000407</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>+1-555-0212</t>
+          <t>081000583</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ross</t>
+          <t>Griffin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Harper</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>benjamin.ross@example.com</t>
+          <t>harper.griffin@office.com</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>+1-555-0113</t>
+          <t>0701000444</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>+1-555-0213</t>
+          <t>081000636</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bryant</t>
+          <t>Hughes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>amelia.bryant@example.com</t>
+          <t>alexander.hughes@office.com</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>+1-555-0114</t>
+          <t>0721000481</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>+1-555-0214</t>
+          <t>081000689</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sanders</t>
+          <t>Perry</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Evelyn</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>henry.sanders@example.com</t>
+          <t>evelyn.perry@office.com</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>+1-555-0115</t>
+          <t>0731000518</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>+1-555-0215</t>
+          <t>081000742</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Griffin</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>harper.griffin@example.com</t>
+          <t>daniel.long@office.com</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>+1-555-0116</t>
+          <t>0761000555</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>+1-555-0216</t>
+          <t>081000795</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hughes</t>
+          <t>Ward</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Abigail</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>alexander.hughes@example.com</t>
+          <t>abigail.ward@office.com</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>+1-555-0117</t>
+          <t>0701000592</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>+1-555-0217</t>
+          <t>081000848</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>Perry</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Evelyn</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>evelyn.perry@example.com</t>
+          <t>matthew.butler@office.com</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>+1-555-0118</t>
+          <t>0721000629</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>+1-555-0218</t>
+          <t>081000901</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>daniel.long@example.com</t>
+          <t>emily.russell@office.com</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>+1-555-0119</t>
+          <t>0731000666</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>+1-555-0219</t>
+          <t>081000954</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Flores</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Abigail</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>abigail.ward@example.com</t>
+          <t>samuel.flores@office.com</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>+1-555-0120</t>
+          <t>0761000703</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>+1-555-0220</t>
+          <t>081001007</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Powell</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -692,29 +692,29 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>matthew.butler@example.com</t>
+          <t>grace.powell@office.com</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>+1-555-0121</t>
+          <t>0701000740</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>+1-555-0221</t>
+          <t>081001060</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Henderson</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>David</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -724,29 +724,29 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>emily.russell@example.com</t>
+          <t>david.henderson@office.com</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>+1-555-0122</t>
+          <t>0721000777</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>+1-555-0222</t>
+          <t>081001113</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>Flores</t>
+          <t>Patterson</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Chloe</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -756,29 +756,29 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>samuel.flores@example.com</t>
+          <t>chloe.patterson@office.com</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>+1-555-0123</t>
+          <t>0731000814</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>+1-555-0223</t>
+          <t>081001166</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Powell</t>
+          <t>Simpson</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -788,29 +788,29 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>grace.powell@example.com</t>
+          <t>joseph.simpson@office.com</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>+1-555-0124</t>
+          <t>0761000851</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>+1-555-0224</t>
+          <t>081001219</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>Henderson</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Zoe</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -820,29 +820,29 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>david.henderson@example.com</t>
+          <t>zoe.alexander@office.com</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>+1-555-0125</t>
+          <t>0701000888</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>+1-555-0225</t>
+          <t>081001272</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>Patterson</t>
+          <t>Jenkins</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -852,145 +852,785 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>chloe.patterson@example.com</t>
+          <t>andrew.jenkins@office.com</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>+1-555-0126</t>
+          <t>0721000925</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>+1-555-0226</t>
+          <t>081001325</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>Simpson</t>
+          <t>Marshall</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>C Sales</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>joseph.simpson@example.com</t>
+          <t>lily.marshall@office.com</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>+1-555-0127</t>
+          <t>0731000962</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>+1-555-0227</t>
+          <t>081001378</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Coleman</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Zoe</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>zoe.alexander@example.com</t>
+          <t>jack.coleman@office.com</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>+1-555-0128</t>
+          <t>0761000999</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>+1-555-0228</t>
+          <t>081001431</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jenkins</t>
+          <t>Ramirez</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Ella</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>andrew.jenkins@example.com</t>
+          <t>ella.ramirez@office.com</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>+1-555-0129</t>
+          <t>0701001036</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>+1-555-0229</t>
+          <t>081001484</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marshall</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Production</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>lily.marshall@example.com</t>
+          <t>owen.bell@office.com</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>+1-555-0130</t>
+          <t>0721001073</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>+1-555-0230</t>
+          <t>081001537</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Scarlett</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>scarlett.ford@office.com</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0731001110</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>081001590</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Leo</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>leo.cox@office.com</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0761001147</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>081001643</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Diaz</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>victoria.diaz@office.com</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0701001184</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>081001696</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Richardson</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Dylan</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>dylan.richardson@office.com</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0721001221</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>081001749</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Reed</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Aria</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>aria.reed@office.com</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0731001258</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>081001802</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cooper</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Nathan</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>C HR</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>nathan.cooper@office.com</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0761001295</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>081001855</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Hannah</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>hannah.ward@office.com</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0701001332</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>081001908</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Morris</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Caleb</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>caleb.morris@office.com</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0721001369</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>081001961</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rogers</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Layla</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>layla.rogers@office.com</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0731001406</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>081002014</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Bailey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Isaac</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>isaac.bailey@office.com</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0761001443</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>081002067</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>nora.cook@office.com</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0701001480</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>081002120</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Murphy</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Julian</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>C Finance</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>julian.murphy@office.com</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0721001517</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>081002173</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Kelly</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>aurora.kelly@office.com</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0731001554</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>081002226</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Howard</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>adrian.howard@office.com</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0761001591</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>081002279</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ward</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Stella</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>stella.ward@office.com</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0701001628</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>081002332</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Peterson</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Wyatt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>wyatt.peterson@office.com</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0721001665</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>081002385</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Levi</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>C Support</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>levi.gray@office.com</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0731001702</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>081002438</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Violet</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>violet.james@office.com</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0761001739</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>081002491</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Watson</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ezra</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>ezra.watson@office.com</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0701001776</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>081002544</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Brooks</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ruby</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>ruby.brooks@office.com</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0721001813</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>081002597</t>
         </is>
       </c>
     </row>

--- a/test-data/test_contacts.xlsx
+++ b/test-data/test_contacts.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>olivia.bennett@office.com</t>
+          <t/>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -308,7 +308,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>charlotte.simmons@office.com</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
